--- a/artfynd/A 41242-2025 artfynd.xlsx
+++ b/artfynd/A 41242-2025 artfynd.xlsx
@@ -767,7 +767,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">

--- a/artfynd/A 41242-2025 artfynd.xlsx
+++ b/artfynd/A 41242-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>98092900</v>
       </c>
       <c r="B2" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607974.9444297323</v>
+        <v>607975</v>
       </c>
       <c r="R2" t="n">
-        <v>6760884.907676795</v>
+        <v>6760885</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -748,19 +743,9 @@
           <t>2021-08-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-08-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,37 +773,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123420152</v>
+        <v>123420154</v>
       </c>
       <c r="B3" t="n">
-        <v>78546</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -828,7 +808,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -837,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607917</v>
+        <v>607975</v>
       </c>
       <c r="R3" t="n">
-        <v>6760865</v>
+        <v>6760898</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +847,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2953</t>
+          <t>2024_2951</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -877,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +887,265 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
+          <t>David Isaksson, Linnéa Kjellberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123420152</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>S Vitrosmuran, Gstr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>607917</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6760865</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hamrånge</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2024_2953</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>David Isaksson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123301234</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skjortnäs, Gstr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>607960</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6760901</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hamrånge</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-08-08</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-08-08</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Samuel Johnson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
         </is>

--- a/artfynd/A 41242-2025 artfynd.xlsx
+++ b/artfynd/A 41242-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98092900</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123420154</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123420152</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1150,8 +1170,19 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123301234</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>